--- a/User_Data.xlsx
+++ b/User_Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,11 +453,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HOÀNG</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4900000</v>
+        <v>1200000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -466,18 +466,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>LAN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1200000</v>
+        <v>3500000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -493,11 +493,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LAN</t>
+          <t>ADMIN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3500000</v>
+        <v>99989999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -506,18 +506,18 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Boss</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADMIN</t>
+          <t>THẢO</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99999999</v>
+        <v>450000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -526,18 +526,18 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>THẢO</t>
+          <t>HÙNG</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>450000</v>
+        <v>7800000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,18 +546,18 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>VIP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HÙNG</t>
+          <t>MAI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7800000</v>
+        <v>2100000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -566,42 +566,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAI</t>
+          <t>JACK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2100000</v>
+        <v>5000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VND</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Foreigner</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JACK</t>
+          <t>ALICE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5000</v>
+        <v>1200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -613,38 +613,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALICE</t>
+          <t>YUKI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1200</v>
+        <v>1270034</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>Foreigner</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>YUKI</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>250000</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>JPY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
         <is>
           <t>Foreigner</t>
         </is>
